--- a/docs/caso-surquillo-modelo-inversion.xlsx
+++ b/docs/caso-surquillo-modelo-inversion.xlsx
@@ -323,7 +323,7 @@
     <t>Plusvalía anualizada optimista</t>
   </si>
   <si>
-    <t>Tip de descarte rápido: Cuidado! Si la plusvalía anual es menor que la inflación del periodo, regularmente la ganancia neta no compensa el riesgo.</t>
+    <t>Chequeo rápido (2 pruebas). 1) ¿La plusvalía anual le gana a la inflación del periodo? Si no, la sola subida de precio no cubre la inflación. 2) ¿El retorno total (plusvalía + alquiler) le gana a un depósito a plazo? Si tampoco, difícil que compense el riesgo. Mirar solo la plusvalía engaña: lo que decide es plusvalía + alquiler frente al depósito.</t>
   </si>
   <si>
     <t>Plusvalía histórica anualizada y tasa de proyección a futuro (regla: usar la menor entre plusvalía histórica e inflación, para ser conservador)</t>
